--- a/SType1.xlsx
+++ b/SType1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AB36BDE-8985-42CB-97D5-45043D83DAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{4AB36BDE-8985-42CB-97D5-45043D83DAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E0F31CD-0772-4711-9AD1-9D306FC1D39E}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{13665051-F481-4A18-A930-FCC6F426C218}"/>
   </bookViews>
@@ -18,28 +18,27 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="Chart_Sektor_name">OFFSET([1]Industri_Unggulan!$B$8,1,1,[1]g!$E$3,1)</definedName>
     <definedName name="Chart_Sektor_x">OFFSET([1]Industri_Unggulan!$F$8,1,1,[1]g!$E$3,1)</definedName>
     <definedName name="Chart_Sektor_y">OFFSET([1]Industri_Unggulan!$E$8,1,1,[1]g!$E$3,1)</definedName>
     <definedName name="cwww10">#REF!</definedName>
-    <definedName name="Industri">[3]K.Supply!$P$2:$P$96</definedName>
-    <definedName name="Kategori">[3]Sheet1!$U$2:$U$18</definedName>
-    <definedName name="Nama_KabKota">[3]Sheet2!$F$2:$F$40</definedName>
-    <definedName name="NamaTabel">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$6"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="Industri">[2]K.Supply!$P$2:$P$96</definedName>
+    <definedName name="Kategori">[2]Sheet1!$U$2:$U$18</definedName>
+    <definedName name="Nama_KabKota">[2]Sheet2!$F$2:$F$40</definedName>
+    <definedName name="NamaTabel">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$6"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="NamaTabelImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$6"),0,0,1,#REF!)</definedName>
-    <definedName name="Produk">[3]K.Supply!$T$2:$T$76</definedName>
-    <definedName name="Tabel">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$"&amp;[3]S2LP!$H$1),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="Produk">[2]K.Supply!$T$2:$T$76</definedName>
+    <definedName name="Tabel">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$"&amp;[2]S2LP!$H$1),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$"&amp;#REF!),0,0,1,#REF!)</definedName>
-    <definedName name="TabelKab">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$"&amp;[3]S2LP!$H$2),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelKab">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$"&amp;[2]S2LP!$H$2),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelKabImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$"&amp;#REF!),0,0,1,#REF!)</definedName>
-    <definedName name="TabelKabTotal">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$170"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelKabTotal">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$170"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelKabTotalImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$293"),0,0,1,#REF!)</definedName>
-    <definedName name="TabelTotal">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$169"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelTotal">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$169"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelTotalImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$292"),0,0,1,#REF!)</definedName>
-    <definedName name="Tahun">[3]Sheet1!$A$2:$A$18</definedName>
+    <definedName name="Tahun">[2]Sheet1!$A$2:$A$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,10 +61,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -272,56 +267,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="IO_2024 (RAW)"/>
-      <sheetName val="Tenaga Kerja"/>
-      <sheetName val="IO-2024 (CEK)"/>
-      <sheetName val="input baris R"/>
-      <sheetName val="PDRB_Kabupaten"/>
-      <sheetName val="PDRB_Padagimo"/>
-      <sheetName val="io"/>
-      <sheetName val="DeskripsiSektor"/>
-      <sheetName val="BAU_Lahan"/>
-      <sheetName val="LAS_Lahan"/>
-      <sheetName val="LDC"/>
-      <sheetName val="SType1"/>
-      <sheetName val="SType2"/>
-      <sheetName val="Stype3"/>
-      <sheetName val="ProyeksiPopulasi"/>
-      <sheetName val="populasiPenduduk"/>
-      <sheetName val="populasiPesisir"/>
-      <sheetName val="PendudukPesisir"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1171,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="2">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="Q4" s="1">
         <v>0</v>
@@ -1233,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>0.15000000000000002</v>
+        <v>0.11</v>
       </c>
       <c r="J5" s="2">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K5" s="2">
         <v>0.01</v>
@@ -1254,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="2">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="Q5" s="1">
         <v>0</v>
@@ -1316,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="J6" s="2">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K6" s="2">
         <v>0.01</v>
@@ -1337,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="2">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -1378,7 +1323,7 @@
         <v>0.05</v>
       </c>
       <c r="B7" s="2">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -1482,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
@@ -1503,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="2">
-        <v>0.55000000000000004</v>
+        <v>0.51</v>
       </c>
       <c r="Q8" s="1">
         <v>0</v>
@@ -1565,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -1731,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J11" s="3">
         <v>0.5</v>
@@ -2259,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T17" s="1">
         <v>0</v>
@@ -2840,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T24" s="1">
         <v>0</v>
@@ -2926,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="T25" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="U25" s="1">
         <v>0</v>
@@ -3009,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="U26" s="1">
         <v>0</v>
@@ -3089,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T27" s="1">
         <v>0</v>
@@ -3172,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T28" s="1">
         <v>0</v>
@@ -3255,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T29" s="1">
         <v>0</v>
@@ -3338,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T30" s="1">
         <v>0</v>
@@ -3421,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T31" s="1">
         <v>0</v>
@@ -3504,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T32" s="1">
         <v>0</v>
@@ -3587,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T33" s="1">
         <v>0</v>
@@ -3670,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T34" s="1">
         <v>0</v>
@@ -3753,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T35" s="1">
         <v>0</v>
@@ -3836,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T36" s="1">
         <v>0</v>
@@ -3919,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="S37" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T37" s="1">
         <v>0</v>
@@ -4002,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="S38" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T38" s="1">
         <v>0</v>
@@ -4085,7 +4030,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T39" s="1">
         <v>0</v>
@@ -4168,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T40" s="1">
         <v>0</v>
@@ -4251,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T41" s="1">
         <v>0</v>
@@ -4334,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T42" s="1">
         <v>0</v>
@@ -4417,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T43" s="1">
         <v>0</v>
@@ -4500,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T44" s="1">
         <v>0</v>
@@ -4583,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T45" s="1">
         <v>0</v>
@@ -4666,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T46" s="1">
         <v>0</v>
@@ -4749,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T47" s="1">
         <v>0</v>
@@ -4832,7 +4777,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T48" s="1">
         <v>0</v>
@@ -4915,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T49" s="1">
         <v>0</v>
@@ -4998,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="S50" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T50" s="1">
         <v>0</v>
@@ -5081,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T51" s="1">
         <v>0</v>
@@ -5164,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T52" s="1">
         <v>0</v>
@@ -5202,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="1">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -5247,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="S53" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T53" s="1">
         <v>0</v>
@@ -5330,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="S54" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T54" s="1">
         <v>0</v>
@@ -5413,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="S55" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T55" s="1">
         <v>0</v>
@@ -5496,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="S56" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T56" s="1">
         <v>0</v>
@@ -5579,7 +5524,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T57" s="1">
         <v>0</v>
@@ -5662,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T58" s="1">
         <v>0</v>
@@ -5745,7 +5690,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T59" s="1">
         <v>0</v>
@@ -5828,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="S60" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T60" s="1">
         <v>0</v>
@@ -5866,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="1">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -5911,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="1">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T61" s="1">
         <v>0</v>
@@ -5943,13 +5888,13 @@
         <v>0.31000000000000005</v>
       </c>
       <c r="B62" s="1">
-        <v>0.42000000000000004</v>
+        <v>0.45000000000000007</v>
       </c>
       <c r="C62" s="1">
         <v>0.9</v>
       </c>
       <c r="D62" s="1">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="E62" s="1">
         <v>0.73</v>
@@ -5964,10 +5909,10 @@
         <v>0</v>
       </c>
       <c r="I62" s="1">
-        <v>0</v>
+        <v>9.9999999999997868E-3</v>
       </c>
       <c r="J62" s="1">
-        <v>0</v>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -5985,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="1">
-        <v>5.9999999999999942E-2</v>
+        <v>0.15999999999999992</v>
       </c>
       <c r="Q62" s="1">
         <v>0.6</v>
@@ -5994,10 +5939,10 @@
         <v>1</v>
       </c>
       <c r="S62" s="1">
-        <v>2.6756756756757594E-2</v>
+        <v>1</v>
       </c>
       <c r="T62" s="1">
-        <v>0.19999999999999996</v>
+        <v>1</v>
       </c>
       <c r="U62" s="1">
         <v>0</v>
@@ -6024,4 +5969,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{747e98d3-0e70-4db5-a56b-cae542e688be}" enabled="0" method="" siteId="{747e98d3-0e70-4db5-a56b-cae542e688be}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/SType1.xlsx
+++ b/SType1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{4AB36BDE-8985-42CB-97D5-45043D83DAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E0F31CD-0772-4711-9AD1-9D306FC1D39E}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{4AB36BDE-8985-42CB-97D5-45043D83DAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4211815B-DED9-4AB0-B353-608F00C11D06}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{13665051-F481-4A18-A930-FCC6F426C218}"/>
   </bookViews>
@@ -1116,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="2">
-        <v>0.11</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="Q4" s="1">
         <v>0</v>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="2">
-        <v>0.11</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="Q5" s="1">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="2">
-        <v>0.11</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -1323,34 +1323,34 @@
         <v>0.05</v>
       </c>
       <c r="B7" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>0.05</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="2">
-        <v>0.51</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="Q8" s="1">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0.1</v>
       </c>
       <c r="K18" s="2">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
@@ -5888,7 +5888,7 @@
         <v>0.31000000000000005</v>
       </c>
       <c r="B62" s="1">
-        <v>0.45000000000000007</v>
+        <v>0.47000000000000008</v>
       </c>
       <c r="C62" s="1">
         <v>0.9</v>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="1">
-        <v>0.15999999999999992</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="1">
         <v>0.6</v>

--- a/SType1.xlsx
+++ b/SType1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{4AB36BDE-8985-42CB-97D5-45043D83DAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4211815B-DED9-4AB0-B353-608F00C11D06}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3C5E09-EC02-4CF7-922F-E5525C4E2340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{13665051-F481-4A18-A930-FCC6F426C218}"/>
   </bookViews>
@@ -84,18 +84,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -111,10 +105,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1070,11 +1062,11 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.05</v>
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1115,8 +1107,8 @@
       <c r="O4" s="1">
         <v>0</v>
       </c>
-      <c r="P4" s="2">
-        <v>0.15000000000000002</v>
+      <c r="P4" s="1">
+        <v>0.1</v>
       </c>
       <c r="Q4" s="1">
         <v>0</v>
@@ -1177,14 +1169,14 @@
       <c r="H5" s="1">
         <v>0</v>
       </c>
-      <c r="I5" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0.01</v>
+      <c r="I5" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
       </c>
       <c r="L5" s="1">
         <v>0</v>
@@ -1198,8 +1190,8 @@
       <c r="O5" s="1">
         <v>0</v>
       </c>
-      <c r="P5" s="2">
-        <v>0.15000000000000002</v>
+      <c r="P5" s="1">
+        <v>0.1</v>
       </c>
       <c r="Q5" s="1">
         <v>0</v>
@@ -1236,122 +1228,122 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>0.05</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B7" s="1">
         <v>0.05</v>
       </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2">
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
-      <c r="T6" s="1">
-        <v>0</v>
-      </c>
-      <c r="U6" s="1">
-        <v>0</v>
-      </c>
-      <c r="V6" s="1">
-        <v>0</v>
-      </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
-      <c r="X6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K7" s="1">
         <v>0.03</v>
       </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0.05</v>
-      </c>
       <c r="L7" s="1">
         <v>0</v>
       </c>
@@ -1402,11 +1394,11 @@
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0.05</v>
+      <c r="A8" s="1">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
@@ -1427,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>0.01</v>
+        <v>0.3</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
@@ -1447,8 +1439,8 @@
       <c r="O8" s="1">
         <v>0</v>
       </c>
-      <c r="P8" s="2">
-        <v>0.55000000000000004</v>
+      <c r="P8" s="1">
+        <v>0.3</v>
       </c>
       <c r="Q8" s="1">
         <v>0</v>
@@ -1509,11 +1501,11 @@
       <c r="H9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="2">
-        <v>0.01</v>
+      <c r="I9" s="1">
+        <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -1651,11 +1643,11 @@
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.05</v>
+      <c r="A11" s="1">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
@@ -1675,11 +1667,11 @@
       <c r="H11" s="1">
         <v>1</v>
       </c>
-      <c r="I11" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0.5</v>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.92</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -1734,11 +1726,11 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.05</v>
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
@@ -1764,8 +1756,8 @@
       <c r="J12" s="1">
         <v>0</v>
       </c>
-      <c r="K12" s="2">
-        <v>0.8</v>
+      <c r="K12" s="1">
+        <v>0.97</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -1817,11 +1809,11 @@
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0.05</v>
+      <c r="A13" s="1">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0</v>
       </c>
       <c r="C13" s="1">
         <v>0</v>
@@ -1924,8 +1916,8 @@
       <c r="H14" s="1">
         <v>0</v>
       </c>
-      <c r="I14" s="2">
-        <v>0.05</v>
+      <c r="I14" s="1">
+        <v>0.3</v>
       </c>
       <c r="J14" s="1">
         <v>0</v>
@@ -2115,13 +2107,13 @@
         <v>0</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="1">
         <v>0</v>
       </c>
       <c r="S16" s="1">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="T16" s="1">
         <v>0</v>
@@ -2173,8 +2165,8 @@
       <c r="H17" s="1">
         <v>0</v>
       </c>
-      <c r="I17" s="2">
-        <v>0.05</v>
+      <c r="I17" s="1">
+        <v>0</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
@@ -2197,8 +2189,8 @@
       <c r="P17" s="1">
         <v>0</v>
       </c>
-      <c r="Q17" s="2">
-        <v>0.1</v>
+      <c r="Q17" s="1">
+        <v>0.01</v>
       </c>
       <c r="R17" s="1">
         <v>0</v>
@@ -2233,10 +2225,10 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="B18" s="2">
-        <v>0.12000000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="B18" s="1">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
@@ -2256,14 +2248,14 @@
       <c r="H18" s="1">
         <v>0</v>
       </c>
-      <c r="I18" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="K18" s="2">
-        <v>0.03</v>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
@@ -2316,10 +2308,10 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="B19" s="2">
-        <v>0.08</v>
+        <v>0.05</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.05</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -2343,10 +2335,10 @@
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
@@ -2367,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="R19" s="1">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="S19" s="1">
         <v>0</v>
@@ -2404,14 +2396,14 @@
       <c r="B20" s="1">
         <v>0</v>
       </c>
-      <c r="C20" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0.1</v>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2471,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="Z20" s="1">
         <v>0</v>
@@ -2493,11 +2485,11 @@
       <c r="D21" s="1">
         <v>0</v>
       </c>
-      <c r="E21" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0.13</v>
+      <c r="E21" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="F21" s="1">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -2542,13 +2534,13 @@
         <v>0</v>
       </c>
       <c r="U21" s="1">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
       </c>
       <c r="W21" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="X21" s="1">
         <v>0</v>
@@ -2625,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="U22" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="V22" s="1">
         <v>0</v>
@@ -2708,10 +2700,10 @@
         <v>0</v>
       </c>
       <c r="U23" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V23" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W23" s="1">
         <v>0</v>
@@ -5885,22 +5877,22 @@
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>0.31000000000000005</v>
+        <v>0.9</v>
       </c>
       <c r="B62" s="1">
-        <v>0.47000000000000008</v>
+        <v>0.83</v>
       </c>
       <c r="C62" s="1">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D62" s="1">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E62" s="1">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="F62" s="1">
-        <v>0.87</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
@@ -5909,10 +5901,10 @@
         <v>0</v>
       </c>
       <c r="I62" s="1">
-        <v>9.9999999999997868E-3</v>
+        <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>8.0000000000000071E-2</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -5933,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="Q62" s="1">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="R62" s="1">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S62" s="1">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="T62" s="1">
         <v>1</v>
@@ -5948,16 +5940,16 @@
         <v>0</v>
       </c>
       <c r="V62" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W62" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X62" s="1">
         <v>1</v>
       </c>
       <c r="Y62" s="1">
-        <v>0.66999999999999993</v>
+        <v>0.8</v>
       </c>
       <c r="Z62" s="1">
         <v>1</v>
